--- a/data/trans_orig/IP05A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102764</t>
+          <t>102645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>117167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110793</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127234</t>
+          <t>126170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218339</t>
+          <t>217625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>239994</t>
+          <t>239856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>21191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42895</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64046</t>
+          <t>63877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141873</t>
+          <t>141066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159474</t>
+          <t>159822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164056</t>
+          <t>163905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181401</t>
+          <t>181799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311011</t>
+          <t>311635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336687</t>
+          <t>336805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>44436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>81693</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>92020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107201</t>
+          <t>107812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106576</t>
+          <t>106542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123244</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>203290</t>
+          <t>204055</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226093</t>
+          <t>225335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36591</t>
+          <t>37275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46053</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135413</t>
+          <t>135818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157912</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140389</t>
+          <t>141050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161695</t>
+          <t>160945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>283465</t>
+          <t>283633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313645</t>
+          <t>314130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38420</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>59032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75760</t>
+          <t>74380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103556</t>
+          <t>101555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>489795</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>526722</t>
+          <t>524523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>542766</t>
+          <t>542024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577775</t>
+          <t>577766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1044001</t>
+          <t>1038047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1092227</t>
+          <t>1090345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122278</t>
+          <t>122655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157524</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>112878</t>
+          <t>112861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>144748</t>
+          <t>145459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>242649</t>
+          <t>244949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>288683</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79156</t>
+          <t>79098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120212</t>
+          <t>119765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>131452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132428</t>
+          <t>133251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145390</t>
+          <t>144613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256644</t>
+          <t>257783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273350</t>
+          <t>273149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36436</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165978</t>
+          <t>165867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182281</t>
+          <t>181958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187136</t>
+          <t>187321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203857</t>
+          <t>203838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358238</t>
+          <t>358066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381391</t>
+          <t>381349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36780</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>57397</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122723</t>
+          <t>121920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137296</t>
+          <t>137043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145944</t>
+          <t>146081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>258682</t>
+          <t>258252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279937</t>
+          <t>279578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53242</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148901</t>
+          <t>150551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171001</t>
+          <t>171597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148494</t>
+          <t>148508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169969</t>
+          <t>169254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>304257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>333908</t>
+          <t>334287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>46239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>60630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86985</t>
+          <t>87994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>575208</t>
+          <t>576110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>608876</t>
+          <t>608635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615946</t>
+          <t>617197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>649228</t>
+          <t>649525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1204146</t>
+          <t>1203438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250115</t>
+          <t>1249263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107794</t>
+          <t>108026</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82243</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112295</t>
+          <t>110869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169595</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>210366</t>
+          <t>210615</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116593</t>
+          <t>116295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127321</t>
+          <t>127658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131777</t>
+          <t>131427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142616</t>
+          <t>142821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253078</t>
+          <t>253471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268477</t>
+          <t>268435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179955</t>
+          <t>180414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192911</t>
+          <t>193331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193646</t>
+          <t>194271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208379</t>
+          <t>208613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>378291</t>
+          <t>378165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398894</t>
+          <t>398114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118063</t>
+          <t>118128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132690</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>134079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150102</t>
+          <t>149360</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257508</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279559</t>
+          <t>279123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164848</t>
+          <t>165577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184043</t>
+          <t>183810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162080</t>
+          <t>162468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180205</t>
+          <t>180302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333162</t>
+          <t>335531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>359012</t>
+          <t>360703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42895</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>42846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>599072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>626683</t>
+          <t>627971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638895</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>668563</t>
+          <t>668334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1246679</t>
+          <t>1246999</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1290319</t>
+          <t>1289294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123801</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>161926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104492</t>
+          <t>105130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113540</t>
+          <t>113704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126839</t>
+          <t>127887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137350</t>
+          <t>137648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237338</t>
+          <t>237153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249610</t>
+          <t>249363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181783</t>
+          <t>181879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222067</t>
+          <t>221496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240231</t>
+          <t>239633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397641</t>
+          <t>396131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418870</t>
+          <t>419114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84763</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172888</t>
+          <t>173073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158058</t>
+          <t>157524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175753</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>235681</t>
+          <t>228512</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>344633</t>
+          <t>343567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102979</t>
+          <t>106918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137731</t>
+          <t>145116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139999</t>
+          <t>139296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153588</t>
+          <t>153668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142119</t>
+          <t>142013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160330</t>
+          <t>159144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288087</t>
+          <t>288135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310430</t>
+          <t>309773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>506069</t>
+          <t>498731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>609467</t>
+          <t>609546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>671444</t>
+          <t>669819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703641</t>
+          <t>702991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1183095</t>
+          <t>1190782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1300444</t>
+          <t>1302075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>153373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88985</t>
+          <t>88332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>210298</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
